--- a/Web/TestCases/Mesas.xlsx
+++ b/Web/TestCases/Mesas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0453FEB-C18D-4FF1-9DE8-047459D289C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47EB208-600B-4A19-8306-F38B18692947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Num</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>pte</t>
   </si>
   <si>
     <t>Tables page home</t>
@@ -69,6 +66,12 @@
   <si>
     <t xml:space="preserve">1. The user clicks "Mesas"
 </t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>No hay datos q mostrar</t>
   </si>
 </sst>
 </file>
@@ -146,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -165,9 +168,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -553,29 +553,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="3"/>
@@ -589,7 +591,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
@@ -603,7 +605,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="3"/>
